--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/随机道具组配置/cfg_erhuanbaoxiang.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/随机道具组配置/cfg_erhuanbaoxiang.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="154">
   <si>
     <t>id</t>
   </si>
@@ -232,10 +232,340 @@
     <t>1#1</t>
   </si>
   <si>
-    <t>0#10000</t>
+    <t>0#10</t>
   </si>
   <si>
     <t>艾利尼斯之怒</t>
+  </si>
+  <si>
+    <t>积分</t>
+  </si>
+  <si>
+    <t>8888#8888</t>
+  </si>
+  <si>
+    <t>0#1</t>
+  </si>
+  <si>
+    <t>1888#1888</t>
+  </si>
+  <si>
+    <t>0#2</t>
+  </si>
+  <si>
+    <t>1588#1588</t>
+  </si>
+  <si>
+    <t>0#3</t>
+  </si>
+  <si>
+    <t>1288#1288</t>
+  </si>
+  <si>
+    <t>0#4</t>
+  </si>
+  <si>
+    <t>588#588</t>
+  </si>
+  <si>
+    <t>0#5</t>
+  </si>
+  <si>
+    <t>388#388</t>
+  </si>
+  <si>
+    <t>0#6</t>
+  </si>
+  <si>
+    <t>288#288</t>
+  </si>
+  <si>
+    <t>0#7</t>
+  </si>
+  <si>
+    <t>188#188</t>
+  </si>
+  <si>
+    <t>0#8</t>
+  </si>
+  <si>
+    <t>88#88</t>
+  </si>
+  <si>
+    <t>0#9</t>
+  </si>
+  <si>
+    <t>100w金币</t>
+  </si>
+  <si>
+    <t>1000000#1000000</t>
+  </si>
+  <si>
+    <t>0#50</t>
+  </si>
+  <si>
+    <t>300w金币</t>
+  </si>
+  <si>
+    <t>3000000#3000000</t>
+  </si>
+  <si>
+    <t>0#40</t>
+  </si>
+  <si>
+    <t>500w金币</t>
+  </si>
+  <si>
+    <t>5000000#5000000</t>
+  </si>
+  <si>
+    <t>0#30</t>
+  </si>
+  <si>
+    <t>1000W金币</t>
+  </si>
+  <si>
+    <t>10000000#10000000</t>
+  </si>
+  <si>
+    <t>0#20</t>
+  </si>
+  <si>
+    <t>卓越的 水之项链</t>
+  </si>
+  <si>
+    <t>卓越的 地之项链</t>
+  </si>
+  <si>
+    <t>卓越的 雷之项链</t>
+  </si>
+  <si>
+    <t>卓越的 火之项链</t>
+  </si>
+  <si>
+    <t>卓越的 冰之项链</t>
+  </si>
+  <si>
+    <t>卓越的 风之项链</t>
+  </si>
+  <si>
+    <t>卓越的 毒之项链</t>
+  </si>
+  <si>
+    <t>卓越的 紫晶项链</t>
+  </si>
+  <si>
+    <t>卓越的 冰之指环</t>
+  </si>
+  <si>
+    <t>卓越的 毒之指环</t>
+  </si>
+  <si>
+    <t>卓越的 火之指环</t>
+  </si>
+  <si>
+    <t>雷鸟术</t>
+  </si>
+  <si>
+    <t>0#15</t>
+  </si>
+  <si>
+    <t>黑龙波术</t>
+  </si>
+  <si>
+    <t>霹雳回旋斩之石</t>
+  </si>
+  <si>
+    <t>治疗之石</t>
+  </si>
+  <si>
+    <t>防御之石</t>
+  </si>
+  <si>
+    <t>攻击之石</t>
+  </si>
+  <si>
+    <t>链雷咒 羊皮纸</t>
+  </si>
+  <si>
+    <t>星云火链 卷轴</t>
+  </si>
+  <si>
+    <t>卓越的 皮盔</t>
+  </si>
+  <si>
+    <t>卓越的 皮铠</t>
+  </si>
+  <si>
+    <t>卓越的 皮护手</t>
+  </si>
+  <si>
+    <t>卓越的 皮护腿</t>
+  </si>
+  <si>
+    <t>卓越的 皮靴</t>
+  </si>
+  <si>
+    <t>卓越的 革盔</t>
+  </si>
+  <si>
+    <t>卓越的 革铠</t>
+  </si>
+  <si>
+    <t>卓越的 革护手</t>
+  </si>
+  <si>
+    <t>卓越的 革护腿</t>
+  </si>
+  <si>
+    <t>卓越的 革靴</t>
+  </si>
+  <si>
+    <t>卓越的 藤盔</t>
+  </si>
+  <si>
+    <t>卓越的 藤铠</t>
+  </si>
+  <si>
+    <t>卓越的 藤护手</t>
+  </si>
+  <si>
+    <t>卓越的 藤护腿</t>
+  </si>
+  <si>
+    <t>卓越的 藤靴</t>
+  </si>
+  <si>
+    <t>幻龙术</t>
+  </si>
+  <si>
+    <t>审判术</t>
+  </si>
+  <si>
+    <t>卓越的 红翼之盔</t>
+  </si>
+  <si>
+    <t>卓越的 红翼之铠</t>
+  </si>
+  <si>
+    <t>卓越的 红翼之护腿</t>
+  </si>
+  <si>
+    <t>卓越的 红翼之靴</t>
+  </si>
+  <si>
+    <t>卓越的 红翼之护手</t>
+  </si>
+  <si>
+    <t>远古之盔</t>
+  </si>
+  <si>
+    <t>卓越的 圣魂之盔</t>
+  </si>
+  <si>
+    <t>卓越的 圣魂之铠</t>
+  </si>
+  <si>
+    <t>卓越的 圣魂护腿</t>
+  </si>
+  <si>
+    <t>卓越的 圣魂之靴</t>
+  </si>
+  <si>
+    <t>卓越的 圣魂护手</t>
+  </si>
+  <si>
+    <t>卓越的 闪光之铠</t>
+  </si>
+  <si>
+    <t>卓越的 闪光护腿</t>
+  </si>
+  <si>
+    <t>卓越的 闪光护手</t>
+  </si>
+  <si>
+    <t>卓越的 闪光之靴</t>
+  </si>
+  <si>
+    <t>卓越的 亚特兰蒂斯之铠</t>
+  </si>
+  <si>
+    <t>卓越的 亚特兰蒂斯之护腿</t>
+  </si>
+  <si>
+    <t>卓越的 亚特兰蒂斯之靴</t>
+  </si>
+  <si>
+    <t>卓越的 亚特兰蒂斯之护手</t>
+  </si>
+  <si>
+    <t>卓越的 传说之靴</t>
+  </si>
+  <si>
+    <t>卓越的 传说之护腿</t>
+  </si>
+  <si>
+    <t>卓越的 传说护手</t>
+  </si>
+  <si>
+    <t>卓越的 传说之铠</t>
+  </si>
+  <si>
+    <t>卓越的 传说之盔</t>
+  </si>
+  <si>
+    <t>卓越的 龙王之靴</t>
+  </si>
+  <si>
+    <t>卓越的 龙王护腿</t>
+  </si>
+  <si>
+    <t>卓越的 龙王护手</t>
+  </si>
+  <si>
+    <t>卓越的 龙王之铠</t>
+  </si>
+  <si>
+    <t>卓越的 龙王之盔</t>
+  </si>
+  <si>
+    <t>9#1</t>
+  </si>
+  <si>
+    <t>9#2</t>
+  </si>
+  <si>
+    <t>9#3</t>
+  </si>
+  <si>
+    <t>9#4</t>
+  </si>
+  <si>
+    <t>9#5</t>
+  </si>
+  <si>
+    <t>9#6</t>
+  </si>
+  <si>
+    <t>50#7</t>
+  </si>
+  <si>
+    <t>50#8</t>
+  </si>
+  <si>
+    <t>50#9</t>
+  </si>
+  <si>
+    <t>99999#50</t>
+  </si>
+  <si>
+    <t>99999#40</t>
+  </si>
+  <si>
+    <t>99999#30</t>
+  </si>
+  <si>
+    <t>99999#20</t>
   </si>
 </sst>
 </file>
@@ -248,7 +578,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -261,6 +591,18 @@
       <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -424,6 +766,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -597,12 +945,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -755,143 +1097,149 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="6">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -904,7 +1252,19 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -959,11 +1319,21 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
     <dxf>
       <fill>
         <patternFill patternType="solid">
           <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1227,160 +1597,161 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5"/>
+  <dimension ref="A1:L93"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="3" max="3" width="17.75" customWidth="1"/>
-    <col min="4" max="4" width="10.375"/>
+    <col min="3" max="3" width="24.5" customWidth="1"/>
+    <col min="4" max="4" width="22.375" customWidth="1"/>
+    <col min="5" max="5" width="28" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="16.5" spans="1:12">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3" t="s">
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" s="2" customFormat="1" ht="102.95" customHeight="1" spans="1:12">
-      <c r="A2" s="5" t="s">
+    <row r="2" s="4" customFormat="1" ht="102.95" customHeight="1" spans="1:12">
+      <c r="A2" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L2" s="6" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="16.5" spans="1:12">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="L3" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" ht="16.5" spans="1:12">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="J4" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="K4" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="L4" s="4" t="s">
+      <c r="L4" s="6" t="s">
         <v>39</v>
       </c>
     </row>
@@ -1391,11 +1762,11 @@
       <c r="B5" s="1">
         <v>1</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D5" s="6">
-        <v>21200101</v>
+      <c r="D5" s="2">
+        <v>2120010199</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>41</v>
@@ -1411,11 +1782,11 @@
       <c r="B6" s="1">
         <v>1</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D6" s="6">
-        <v>21200111</v>
+      <c r="D6" s="2">
+        <v>2120011199</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>41</v>
@@ -1424,12 +1795,1973 @@
         <v>42</v>
       </c>
     </row>
+    <row r="7" ht="16.5" spans="1:12">
+      <c r="A7" s="1">
+        <v>3</v>
+      </c>
+      <c r="B7" s="1">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" s="2">
+        <v>10240001</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" ht="16.5" spans="1:12">
+      <c r="A8" s="1">
+        <v>4</v>
+      </c>
+      <c r="B8" s="1">
+        <v>1</v>
+      </c>
+      <c r="C8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="2">
+        <v>10240001</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9" ht="16.5" spans="1:12">
+      <c r="A9" s="1">
+        <v>5</v>
+      </c>
+      <c r="B9" s="1">
+        <v>1</v>
+      </c>
+      <c r="C9" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" s="2">
+        <v>10240001</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F9" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" ht="16.5" spans="1:12">
+      <c r="A10" s="1">
+        <v>6</v>
+      </c>
+      <c r="B10" s="1">
+        <v>1</v>
+      </c>
+      <c r="C10" t="s">
+        <v>44</v>
+      </c>
+      <c r="D10" s="2">
+        <v>10240001</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F10" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="11" ht="16.5" spans="1:12">
+      <c r="A11" s="1">
+        <v>7</v>
+      </c>
+      <c r="B11" s="1">
+        <v>1</v>
+      </c>
+      <c r="C11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" s="2">
+        <v>10240001</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F11" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="12" ht="16.5" spans="1:12">
+      <c r="A12" s="1">
+        <v>8</v>
+      </c>
+      <c r="B12" s="1">
+        <v>1</v>
+      </c>
+      <c r="C12" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="2">
+        <v>10240001</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F12" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13" ht="16.5" spans="1:12">
+      <c r="A13" s="1">
+        <v>9</v>
+      </c>
+      <c r="B13" s="1">
+        <v>1</v>
+      </c>
+      <c r="C13" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" s="2">
+        <v>10240001</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F13" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" ht="16.5" spans="1:12">
+      <c r="A14" s="1">
+        <v>10</v>
+      </c>
+      <c r="B14" s="1">
+        <v>1</v>
+      </c>
+      <c r="C14" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" s="2">
+        <v>10240001</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F14" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" ht="16.5" spans="1:12">
+      <c r="A15" s="1">
+        <v>11</v>
+      </c>
+      <c r="B15" s="1">
+        <v>1</v>
+      </c>
+      <c r="C15" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" s="2">
+        <v>10240001</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F15" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="16" ht="16.5" spans="1:12">
+      <c r="A16" s="1">
+        <v>12</v>
+      </c>
+      <c r="B16" s="1">
+        <v>1</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D16" s="2">
+        <v>10010001</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="17" ht="16.5" spans="1:6">
+      <c r="A17" s="1">
+        <v>13</v>
+      </c>
+      <c r="B17" s="1">
+        <v>1</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D17" s="2">
+        <v>10010001</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="18" ht="16.5" spans="1:6">
+      <c r="A18" s="1">
+        <v>14</v>
+      </c>
+      <c r="B18" s="1">
+        <v>1</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D18" s="2">
+        <v>10010001</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="19" ht="16.5" spans="1:6">
+      <c r="A19" s="1">
+        <v>15</v>
+      </c>
+      <c r="B19" s="1">
+        <v>1</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D19" s="2">
+        <v>10010001</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="20" ht="16.5" spans="1:6">
+      <c r="A20" s="1">
+        <v>16</v>
+      </c>
+      <c r="B20" s="1">
+        <v>1</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D20" s="8">
+        <v>2100020199</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F20" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="21" ht="16.5" spans="1:6">
+      <c r="A21" s="1">
+        <v>17</v>
+      </c>
+      <c r="B21" s="1">
+        <v>1</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D21" s="8">
+        <v>2100020299</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F21" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="22" ht="16.5" spans="1:6">
+      <c r="A22" s="1">
+        <v>18</v>
+      </c>
+      <c r="B22" s="1">
+        <v>1</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D22" s="8">
+        <v>2100020399</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F22" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="23" ht="16.5" spans="1:6">
+      <c r="A23" s="1">
+        <v>19</v>
+      </c>
+      <c r="B23" s="1">
+        <v>1</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D23" s="8">
+        <v>2100020499</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F23" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="24" ht="16.5" spans="1:6">
+      <c r="A24" s="1">
+        <v>20</v>
+      </c>
+      <c r="B24" s="1">
+        <v>1</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D24" s="8">
+        <v>2100020599</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F24" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="25" ht="16.5" spans="1:6">
+      <c r="A25" s="1">
+        <v>21</v>
+      </c>
+      <c r="B25" s="1">
+        <v>1</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D25" s="8">
+        <v>2100020699</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F25" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="26" ht="16.5" spans="1:6">
+      <c r="A26" s="1">
+        <v>22</v>
+      </c>
+      <c r="B26" s="1">
+        <v>1</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D26" s="8">
+        <v>2100020799</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F26" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="27" ht="16.5" spans="1:6">
+      <c r="A27" s="1">
+        <v>23</v>
+      </c>
+      <c r="B27" s="1">
+        <v>1</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D27" s="8">
+        <v>2100020899</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F27" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="28" ht="16.5" spans="1:6">
+      <c r="A28" s="1">
+        <v>24</v>
+      </c>
+      <c r="B28" s="1">
+        <v>1</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D28" s="3">
+        <v>2110001299</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F28" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="29" ht="16.5" spans="1:6">
+      <c r="A29" s="1">
+        <v>25</v>
+      </c>
+      <c r="B29" s="1">
+        <v>1</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D29" s="3">
+        <v>2110002299</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F29" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="30" ht="16.5" spans="1:6">
+      <c r="A30" s="1">
+        <v>26</v>
+      </c>
+      <c r="B30" s="1">
+        <v>1</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D30" s="3">
+        <v>2110003299</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F30" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="31" ht="16.5" spans="1:6">
+      <c r="A31" s="1">
+        <v>27</v>
+      </c>
+      <c r="B31" s="1">
+        <v>1</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D31" s="8">
+        <v>2100020199</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F31" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="32" ht="16.5" spans="1:6">
+      <c r="A32" s="1">
+        <v>28</v>
+      </c>
+      <c r="B32" s="1">
+        <v>1</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D32" s="8">
+        <v>2100020299</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F32" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="33" ht="16.5" spans="1:6">
+      <c r="A33" s="1">
+        <v>29</v>
+      </c>
+      <c r="B33" s="1">
+        <v>1</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D33" s="8">
+        <v>2100020399</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F33" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="34" ht="16.5" spans="1:6">
+      <c r="A34" s="1">
+        <v>30</v>
+      </c>
+      <c r="B34" s="1">
+        <v>1</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D34" s="8">
+        <v>2100020499</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F34" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="35" ht="16.5" spans="1:6">
+      <c r="A35" s="1">
+        <v>31</v>
+      </c>
+      <c r="B35" s="1">
+        <v>1</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D35" s="8">
+        <v>2100020599</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F35" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="36" ht="16.5" spans="1:6">
+      <c r="A36" s="1">
+        <v>32</v>
+      </c>
+      <c r="B36" s="1">
+        <v>1</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D36" s="8">
+        <v>2100020699</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F36" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="37" ht="16.5" spans="1:6">
+      <c r="A37" s="1">
+        <v>33</v>
+      </c>
+      <c r="B37" s="1">
+        <v>1</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D37" s="8">
+        <v>2100020799</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F37" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="38" ht="16.5" spans="1:6">
+      <c r="A38" s="1">
+        <v>34</v>
+      </c>
+      <c r="B38" s="1">
+        <v>1</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D38" s="8">
+        <v>2100020899</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F38" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="39" ht="16.5" spans="1:6">
+      <c r="A39" s="1">
+        <v>35</v>
+      </c>
+      <c r="B39" s="1">
+        <v>1</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D39" s="3">
+        <v>2100001299</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F39" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="40" ht="16.5" spans="1:6">
+      <c r="A40" s="1">
+        <v>36</v>
+      </c>
+      <c r="B40" s="1">
+        <v>1</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D40" s="3">
+        <v>1100700399</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F40" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="41" ht="16.5" spans="1:6">
+      <c r="A41" s="1">
+        <v>37</v>
+      </c>
+      <c r="B41" s="1">
+        <v>1</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D41" s="3">
+        <v>1263000999</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F41" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="42" ht="16.5" spans="1:6">
+      <c r="A42" s="1">
+        <v>38</v>
+      </c>
+      <c r="B42" s="1">
+        <v>1</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D42" s="3">
+        <v>1263002299</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F42" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="43" ht="16.5" spans="1:6">
+      <c r="A43" s="1">
+        <v>39</v>
+      </c>
+      <c r="B43" s="1">
+        <v>1</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D43" s="3">
+        <v>1263002799</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F43" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="44" ht="16.5" spans="1:6">
+      <c r="A44" s="1">
+        <v>40</v>
+      </c>
+      <c r="B44" s="1">
+        <v>1</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D44" s="3">
+        <v>1263002899</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F44" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="45" ht="16.5" spans="1:6">
+      <c r="A45" s="1">
+        <v>41</v>
+      </c>
+      <c r="B45" s="1">
+        <v>1</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D45" s="3">
+        <v>1263002999</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F45" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="46" ht="16.5" spans="1:6">
+      <c r="A46" s="1">
+        <v>42</v>
+      </c>
+      <c r="B46" s="1">
+        <v>1</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D46" s="3">
+        <v>1263508399</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F46" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="47" ht="16.5" spans="1:6">
+      <c r="A47" s="1">
+        <v>43</v>
+      </c>
+      <c r="B47" s="1">
+        <v>1</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D47" s="3">
+        <v>1263510099</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F47" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="48" ht="16.5" spans="1:6">
+      <c r="A48" s="1">
+        <v>44</v>
+      </c>
+      <c r="B48" s="1">
+        <v>1</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D48" s="3">
+        <v>2041012199</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F48" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="49" ht="16.5" spans="1:6">
+      <c r="A49" s="1">
+        <v>45</v>
+      </c>
+      <c r="B49" s="1">
+        <v>1</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D49" s="3">
+        <v>2061012199</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F49" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="50" ht="16.5" spans="1:6">
+      <c r="A50" s="1">
+        <v>46</v>
+      </c>
+      <c r="B50" s="1">
+        <v>1</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D50" s="3">
+        <v>2071012199</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F50" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="51" ht="16.5" spans="1:6">
+      <c r="A51" s="1">
+        <v>47</v>
+      </c>
+      <c r="B51" s="1">
+        <v>1</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D51" s="3">
+        <v>2081012199</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F51" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="52" ht="16.5" spans="1:6">
+      <c r="A52" s="1">
+        <v>48</v>
+      </c>
+      <c r="B52" s="1">
+        <v>1</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D52" s="3">
+        <v>2091012199</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F52" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="53" ht="16.5" spans="1:6">
+      <c r="A53" s="1">
+        <v>49</v>
+      </c>
+      <c r="B53" s="1">
+        <v>1</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D53" s="3">
+        <v>2042012199</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F53" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="54" ht="16.5" spans="1:6">
+      <c r="A54" s="1">
+        <v>50</v>
+      </c>
+      <c r="B54" s="1">
+        <v>1</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D54" s="3">
+        <v>2062012199</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F54" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="55" ht="16.5" spans="1:6">
+      <c r="A55" s="1">
+        <v>51</v>
+      </c>
+      <c r="B55" s="1">
+        <v>1</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D55" s="3">
+        <v>2072012199</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F55" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="56" ht="16.5" spans="1:6">
+      <c r="A56" s="1">
+        <v>52</v>
+      </c>
+      <c r="B56" s="1">
+        <v>1</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D56" s="3">
+        <v>2082012199</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F56" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="57" ht="16.5" spans="1:6">
+      <c r="A57" s="1">
+        <v>53</v>
+      </c>
+      <c r="B57" s="1">
+        <v>1</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D57" s="3">
+        <v>2092012199</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F57" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="58" ht="16.5" spans="1:6">
+      <c r="A58" s="1">
+        <v>54</v>
+      </c>
+      <c r="B58" s="1">
+        <v>1</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D58" s="3">
+        <v>2043012199</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F58" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="59" ht="16.5" spans="1:6">
+      <c r="A59" s="1">
+        <v>55</v>
+      </c>
+      <c r="B59" s="1">
+        <v>1</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D59" s="3">
+        <v>2063012199</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F59" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="60" ht="16.5" spans="1:6">
+      <c r="A60" s="1">
+        <v>56</v>
+      </c>
+      <c r="B60" s="1">
+        <v>1</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D60" s="3">
+        <v>2073012199</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F60" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="61" ht="16.5" spans="1:6">
+      <c r="A61" s="1">
+        <v>57</v>
+      </c>
+      <c r="B61" s="1">
+        <v>1</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D61" s="3">
+        <v>2083012199</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F61" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="62" ht="16.5" spans="1:6">
+      <c r="A62" s="1">
+        <v>58</v>
+      </c>
+      <c r="B62" s="1">
+        <v>1</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D62" s="3">
+        <v>2093012199</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F62" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="63" ht="16.5" spans="1:6">
+      <c r="A63" s="1">
+        <v>59</v>
+      </c>
+      <c r="B63" s="1">
+        <v>1</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D63" s="3">
+        <v>1100700199</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F63" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="64" ht="16.5" spans="1:6">
+      <c r="A64" s="1">
+        <v>60</v>
+      </c>
+      <c r="B64" s="1">
+        <v>1</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D64" s="3">
+        <v>1100700299</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F64" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="65" ht="16.5" spans="1:6">
+      <c r="A65" s="1">
+        <v>61</v>
+      </c>
+      <c r="B65" s="1">
+        <v>1</v>
+      </c>
+      <c r="C65" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="D65" s="10">
+        <v>2066052199</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F65" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="66" ht="16.5" spans="1:6">
+      <c r="A66" s="1">
+        <v>62</v>
+      </c>
+      <c r="B66" s="1">
+        <v>1</v>
+      </c>
+      <c r="C66" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="D66" s="10">
+        <v>2066052299</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F66" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="67" ht="16.5" spans="1:6">
+      <c r="A67" s="1">
+        <v>63</v>
+      </c>
+      <c r="B67" s="1">
+        <v>1</v>
+      </c>
+      <c r="C67" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D67" s="10">
+        <v>2066052399</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F67" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="68" ht="16.5" spans="1:6">
+      <c r="A68" s="1">
+        <v>64</v>
+      </c>
+      <c r="B68" s="1">
+        <v>1</v>
+      </c>
+      <c r="C68" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="D68" s="10">
+        <v>2066052499</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F68" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="69" ht="16.5" spans="1:6">
+      <c r="A69" s="1">
+        <v>65</v>
+      </c>
+      <c r="B69" s="1">
+        <v>1</v>
+      </c>
+      <c r="C69" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="D69" s="10">
+        <v>2066052599</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F69" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="70" ht="16.5" spans="1:6">
+      <c r="A70" s="1">
+        <v>66</v>
+      </c>
+      <c r="B70" s="1">
+        <v>1</v>
+      </c>
+      <c r="C70" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="D70" s="10">
+        <v>2066061199</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F70" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="71" ht="16.5" spans="1:6">
+      <c r="A71" s="1">
+        <v>67</v>
+      </c>
+      <c r="B71" s="1">
+        <v>1</v>
+      </c>
+      <c r="C71" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="D71" s="2">
+        <v>2055052199</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F71" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="72" ht="16.5" spans="1:6">
+      <c r="A72" s="1">
+        <v>68</v>
+      </c>
+      <c r="B72" s="1">
+        <v>1</v>
+      </c>
+      <c r="C72" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="D72" s="2">
+        <v>2055052299</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F72" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="73" ht="16.5" spans="1:6">
+      <c r="A73" s="1">
+        <v>69</v>
+      </c>
+      <c r="B73" s="1">
+        <v>1</v>
+      </c>
+      <c r="C73" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="D73" s="2">
+        <v>2055052399</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F73" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="74" ht="16.5" spans="1:6">
+      <c r="A74" s="1">
+        <v>70</v>
+      </c>
+      <c r="B74" s="1">
+        <v>1</v>
+      </c>
+      <c r="C74" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="D74" s="2">
+        <v>2055052499</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F74" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="75" ht="16.5" spans="1:6">
+      <c r="A75" s="1">
+        <v>71</v>
+      </c>
+      <c r="B75" s="1">
+        <v>1</v>
+      </c>
+      <c r="C75" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="D75" s="2">
+        <v>2055052599</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F75" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="76" ht="16.5" spans="1:6">
+      <c r="A76" s="1">
+        <v>72</v>
+      </c>
+      <c r="B76" s="1">
+        <v>1</v>
+      </c>
+      <c r="C76" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="D76" s="12">
+        <v>2067022199</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F76" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="77" ht="16.5" spans="1:6">
+      <c r="A77" s="1">
+        <v>73</v>
+      </c>
+      <c r="B77" s="1">
+        <v>1</v>
+      </c>
+      <c r="C77" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="D77" s="12">
+        <v>2087022199</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F77" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="78" ht="16.5" spans="1:6">
+      <c r="A78" s="1">
+        <v>74</v>
+      </c>
+      <c r="B78" s="1">
+        <v>1</v>
+      </c>
+      <c r="C78" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="D78" s="12">
+        <v>2077022199</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F78" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="79" ht="16.5" spans="1:6">
+      <c r="A79" s="1">
+        <v>75</v>
+      </c>
+      <c r="B79" s="1">
+        <v>1</v>
+      </c>
+      <c r="C79" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="D79" s="12">
+        <v>2097022199</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F79" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="80" ht="16.5" spans="1:6">
+      <c r="A80" s="1">
+        <v>76</v>
+      </c>
+      <c r="B80" s="1">
+        <v>1</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D80" s="3">
+        <v>1280034199</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F80" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="81" ht="16.5" spans="1:6">
+      <c r="A81" s="1">
+        <v>77</v>
+      </c>
+      <c r="B81" s="1">
+        <v>1</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D81" s="3">
+        <v>1280034299</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F81" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="82" ht="16.5" spans="1:6">
+      <c r="A82" s="1">
+        <v>78</v>
+      </c>
+      <c r="B82" s="1">
+        <v>1</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D82" s="3">
+        <v>1280034399</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F82" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="83" ht="16.5" spans="1:6">
+      <c r="A83" s="1">
+        <v>79</v>
+      </c>
+      <c r="B83" s="1">
+        <v>1</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D83" s="3">
+        <v>1280034499</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F83" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="84" ht="16.5" spans="1:6">
+      <c r="A84" s="1">
+        <v>80</v>
+      </c>
+      <c r="B84" s="1">
+        <v>1</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D84" s="3">
+        <v>2092042199</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F84" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="85" ht="16.5" spans="1:6">
+      <c r="A85" s="1">
+        <v>81</v>
+      </c>
+      <c r="B85" s="1">
+        <v>1</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D85" s="3">
+        <v>2082042199</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F85" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="86" ht="16.5" spans="1:6">
+      <c r="A86" s="1">
+        <v>82</v>
+      </c>
+      <c r="B86" s="1">
+        <v>1</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D86" s="3">
+        <v>2072042199</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F86" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="87" ht="16.5" spans="1:6">
+      <c r="A87" s="1">
+        <v>83</v>
+      </c>
+      <c r="B87" s="1">
+        <v>1</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="D87" s="3">
+        <v>2062042199</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F87" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="88" ht="16.5" spans="1:6">
+      <c r="A88" s="1">
+        <v>84</v>
+      </c>
+      <c r="B88" s="1">
+        <v>1</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D88" s="3">
+        <v>2042042199</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F88" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="89" ht="16.5" spans="1:6">
+      <c r="A89" s="1">
+        <v>85</v>
+      </c>
+      <c r="B89" s="1">
+        <v>1</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D89" s="3">
+        <v>2091042199</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F89" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="90" ht="16.5" spans="1:6">
+      <c r="A90" s="1">
+        <v>86</v>
+      </c>
+      <c r="B90" s="1">
+        <v>1</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D90" s="3">
+        <v>2081042199</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F90" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="91" ht="16.5" spans="1:6">
+      <c r="A91" s="1">
+        <v>87</v>
+      </c>
+      <c r="B91" s="1">
+        <v>1</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D91" s="3">
+        <v>2071042199</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F91" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="92" ht="16.5" spans="1:6">
+      <c r="A92" s="1">
+        <v>88</v>
+      </c>
+      <c r="B92" s="1">
+        <v>1</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D92" s="3">
+        <v>2061042199</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F92" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="93" ht="16.5" spans="1:6">
+      <c r="A93" s="1">
+        <v>89</v>
+      </c>
+      <c r="B93" s="1">
+        <v>1</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D93" s="3">
+        <v>2041042199</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F93" t="s">
+        <v>74</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="D5">
+    <cfRule type="duplicateValues" dxfId="0" priority="67"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D6">
+    <cfRule type="duplicateValues" dxfId="0" priority="66"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D7">
+    <cfRule type="duplicateValues" dxfId="0" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="49"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E7">
+    <cfRule type="duplicateValues" dxfId="0" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="51"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C16">
+    <cfRule type="duplicateValues" dxfId="1" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="56"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D28">
+    <cfRule type="duplicateValues" dxfId="1" priority="120"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="121"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D29">
+    <cfRule type="duplicateValues" dxfId="1" priority="118"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="119"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D30">
+    <cfRule type="duplicateValues" dxfId="1" priority="116"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="117"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D39">
+    <cfRule type="duplicateValues" dxfId="1" priority="110"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="111"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D40">
+    <cfRule type="duplicateValues" dxfId="1" priority="108"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="109"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D41">
+    <cfRule type="duplicateValues" dxfId="1" priority="106"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="107"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D42">
+    <cfRule type="duplicateValues" dxfId="1" priority="104"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="105"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D46">
+    <cfRule type="duplicateValues" dxfId="1" priority="100"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="101"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D47">
+    <cfRule type="duplicateValues" dxfId="1" priority="98"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="99"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D48">
+    <cfRule type="duplicateValues" dxfId="1" priority="96"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="97"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D49">
+    <cfRule type="duplicateValues" dxfId="1" priority="94"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="95"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D50">
+    <cfRule type="duplicateValues" dxfId="1" priority="92"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="93"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D51">
+    <cfRule type="duplicateValues" dxfId="1" priority="90"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="91"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D52">
+    <cfRule type="duplicateValues" dxfId="1" priority="88"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="89"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D53">
+    <cfRule type="duplicateValues" dxfId="1" priority="86"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="87"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D54">
+    <cfRule type="duplicateValues" dxfId="1" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="85"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D55">
+    <cfRule type="duplicateValues" dxfId="1" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="83"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D56">
+    <cfRule type="duplicateValues" dxfId="1" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="81"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D57">
+    <cfRule type="duplicateValues" dxfId="1" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="79"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D58">
+    <cfRule type="duplicateValues" dxfId="1" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="77"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D59">
+    <cfRule type="duplicateValues" dxfId="1" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="75"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D60">
+    <cfRule type="duplicateValues" dxfId="1" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="73"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D61">
+    <cfRule type="duplicateValues" dxfId="1" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="71"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D62">
+    <cfRule type="duplicateValues" dxfId="1" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="69"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D63">
+    <cfRule type="duplicateValues" dxfId="0" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="47"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D64">
+    <cfRule type="duplicateValues" dxfId="0" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="45"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C70">
+    <cfRule type="duplicateValues" dxfId="1" priority="37"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D70">
+    <cfRule type="duplicateValues" dxfId="0" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="39"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E70">
+    <cfRule type="duplicateValues" dxfId="1" priority="43"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D84">
+    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D85">
+    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D86">
+    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D87">
+    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D88">
+    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D89">
+    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D90">
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D91">
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D92">
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D93">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D6">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C17:C19">
+    <cfRule type="duplicateValues" dxfId="1" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="54"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C65:C69">
+    <cfRule type="duplicateValues" dxfId="1" priority="38"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D5:D6">
+    <cfRule type="duplicateValues" dxfId="1" priority="65"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8:D15">
+    <cfRule type="duplicateValues" dxfId="1" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="62"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D16:D19">
+    <cfRule type="duplicateValues" dxfId="1" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="58"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D20:D27">
+    <cfRule type="duplicateValues" dxfId="0" priority="122"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D31:D38">
+    <cfRule type="duplicateValues" dxfId="0" priority="112"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D43:D45">
+    <cfRule type="duplicateValues" dxfId="1" priority="102"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="103"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D65:D69">
+    <cfRule type="duplicateValues" dxfId="0" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="41"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D71:D75">
+    <cfRule type="duplicateValues" dxfId="0" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="35"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D76:D79">
+    <cfRule type="duplicateValues" dxfId="1" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="34"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D80:D83">
+    <cfRule type="duplicateValues" dxfId="0" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E8:E15">
+    <cfRule type="duplicateValues" dxfId="1" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="64"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E16:E19">
+    <cfRule type="duplicateValues" dxfId="1" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="60"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E65:E69">
+    <cfRule type="duplicateValues" dxfId="1" priority="44"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -1440,9 +3772,294 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <sheetData>
+    <row r="1" ht="16.5" spans="1:6">
+      <c r="A1" s="1">
+        <v>3</v>
+      </c>
+      <c r="B1" s="1">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1" s="2">
+        <v>10240001</v>
+      </c>
+      <c r="E1" s="3">
+        <v>18888</v>
+      </c>
+      <c r="F1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="2" ht="16.5" spans="1:6">
+      <c r="A2" s="1">
+        <v>4</v>
+      </c>
+      <c r="B2" s="1">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D2" s="2">
+        <v>10240001</v>
+      </c>
+      <c r="E2" s="3">
+        <v>8888</v>
+      </c>
+      <c r="F2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="3" ht="16.5" spans="1:6">
+      <c r="A3" s="1">
+        <v>5</v>
+      </c>
+      <c r="B3" s="1">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D3" s="2">
+        <v>10240001</v>
+      </c>
+      <c r="E3" s="3">
+        <v>5888</v>
+      </c>
+      <c r="F3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="4" ht="16.5" spans="1:6">
+      <c r="A4" s="1">
+        <v>6</v>
+      </c>
+      <c r="B4" s="1">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4" s="2">
+        <v>10240001</v>
+      </c>
+      <c r="E4" s="3">
+        <v>3888</v>
+      </c>
+      <c r="F4" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="5" ht="16.5" spans="1:6">
+      <c r="A5" s="1">
+        <v>7</v>
+      </c>
+      <c r="B5" s="1">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D5" s="2">
+        <v>10240001</v>
+      </c>
+      <c r="E5" s="3">
+        <v>2888</v>
+      </c>
+      <c r="F5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="6" ht="16.5" spans="1:6">
+      <c r="A6" s="1">
+        <v>8</v>
+      </c>
+      <c r="B6" s="1">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" s="2">
+        <v>10240001</v>
+      </c>
+      <c r="E6" s="3">
+        <v>1888</v>
+      </c>
+      <c r="F6" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="7" ht="16.5" spans="1:6">
+      <c r="A7" s="1">
+        <v>9</v>
+      </c>
+      <c r="B7" s="1">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" s="2">
+        <v>10240001</v>
+      </c>
+      <c r="E7" s="3">
+        <v>888</v>
+      </c>
+      <c r="F7" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="8" ht="16.5" spans="1:6">
+      <c r="A8" s="1">
+        <v>10</v>
+      </c>
+      <c r="B8" s="1">
+        <v>1</v>
+      </c>
+      <c r="C8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="2">
+        <v>10240001</v>
+      </c>
+      <c r="E8" s="3">
+        <v>588</v>
+      </c>
+      <c r="F8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="9" ht="16.5" spans="1:6">
+      <c r="A9" s="1">
+        <v>11</v>
+      </c>
+      <c r="B9" s="1">
+        <v>1</v>
+      </c>
+      <c r="C9" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" s="2">
+        <v>10240001</v>
+      </c>
+      <c r="E9" s="3">
+        <v>188</v>
+      </c>
+      <c r="F9" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="10" ht="16.5" spans="1:6">
+      <c r="A10" s="1">
+        <v>13</v>
+      </c>
+      <c r="B10" s="1">
+        <v>1</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D10" s="2">
+        <v>10010001</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1000000</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="11" ht="16.5" spans="1:6">
+      <c r="A11" s="1">
+        <v>14</v>
+      </c>
+      <c r="B11" s="1">
+        <v>1</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D11" s="2">
+        <v>10010001</v>
+      </c>
+      <c r="E11" s="3">
+        <v>3000000</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="12" ht="16.5" spans="1:6">
+      <c r="A12" s="1">
+        <v>15</v>
+      </c>
+      <c r="B12" s="1">
+        <v>1</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D12" s="2">
+        <v>10010001</v>
+      </c>
+      <c r="E12" s="3">
+        <v>5000000</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="13" ht="16.5" spans="1:6">
+      <c r="A13" s="1">
+        <v>16</v>
+      </c>
+      <c r="B13" s="1">
+        <v>1</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D13" s="2">
+        <v>10010001</v>
+      </c>
+      <c r="E13" s="3">
+        <v>10000000</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="C10">
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C11:C13">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D1:D9">
+    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D10:D13">
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E1:E9">
+    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E10:E13">
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="7"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>

--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/随机道具组配置/cfg_erhuanbaoxiang.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/随机道具组配置/cfg_erhuanbaoxiang.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="195">
   <si>
     <t>id</t>
   </si>
@@ -529,6 +529,129 @@
     <t>卓越的 龙王之盔</t>
   </si>
   <si>
+    <t>卓越的 暗黑斗神之盔</t>
+  </si>
+  <si>
+    <t>卓越的 暗黑斗神之铠</t>
+  </si>
+  <si>
+    <t>卓越的 暗黑斗神护腿</t>
+  </si>
+  <si>
+    <t>卓越的 暗黑斗神护手</t>
+  </si>
+  <si>
+    <t>卓越的 暗黑斗神之靴</t>
+  </si>
+  <si>
+    <t>卓越的 法魂玄灵之盔</t>
+  </si>
+  <si>
+    <t>卓越的 法魂玄灵之铠</t>
+  </si>
+  <si>
+    <t>卓越的 法魂玄灵护腿</t>
+  </si>
+  <si>
+    <t>卓越的 法魂玄灵护手</t>
+  </si>
+  <si>
+    <t>卓越的 法魂玄灵之靴</t>
+  </si>
+  <si>
+    <t>卓越的 紫灵之盔</t>
+  </si>
+  <si>
+    <t>卓越的 紫灵之铠</t>
+  </si>
+  <si>
+    <t>卓越的 紫灵护腿</t>
+  </si>
+  <si>
+    <t>卓越的 紫灵护手</t>
+  </si>
+  <si>
+    <t>卓越的 紫灵之靴</t>
+  </si>
+  <si>
+    <t>卓越的 天魔斗神之铠</t>
+  </si>
+  <si>
+    <t>卓越的 天魔斗神护腿</t>
+  </si>
+  <si>
+    <t>卓越的 天魔斗神护手</t>
+  </si>
+  <si>
+    <t>卓越的 天魔斗神之靴</t>
+  </si>
+  <si>
+    <t>卓越的 断月之光</t>
+  </si>
+  <si>
+    <t>卓越的 龙骨巨晶剑</t>
+  </si>
+  <si>
+    <t>卓越的 魔神剑</t>
+  </si>
+  <si>
+    <t>卓越的 傲天魔剑</t>
+  </si>
+  <si>
+    <t>卓越的 铰刀</t>
+  </si>
+  <si>
+    <t>卓越的 傲视魔弓</t>
+  </si>
+  <si>
+    <t>卓越的 紫焰之弓</t>
+  </si>
+  <si>
+    <t>卓越的 死神之杖</t>
+  </si>
+  <si>
+    <t>卓越的 恒翼之仗</t>
+  </si>
+  <si>
+    <t>卓越的 野望之盾</t>
+  </si>
+  <si>
+    <t>卓越的 独裁权杖</t>
+  </si>
+  <si>
+    <t>卓越的 风影之盔</t>
+  </si>
+  <si>
+    <t>卓越的 风影之铠</t>
+  </si>
+  <si>
+    <t>卓越的 风影之护腿</t>
+  </si>
+  <si>
+    <t>卓越的 风影之靴</t>
+  </si>
+  <si>
+    <t>卓越的 风影之护手</t>
+  </si>
+  <si>
+    <t>卓越的 宙斯之盔</t>
+  </si>
+  <si>
+    <t>卓越的 宙斯之铠</t>
+  </si>
+  <si>
+    <t>卓越的 宙斯护腿</t>
+  </si>
+  <si>
+    <t>卓越的 宙斯之靴</t>
+  </si>
+  <si>
+    <t>卓越的 宙斯护手</t>
+  </si>
+  <si>
+    <t>卓越的 智慧魔典</t>
+  </si>
+  <si>
     <t>9#1</t>
   </si>
   <si>
@@ -578,7 +701,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -603,6 +726,27 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="0"/>
     </font>
     <font>
       <u/>
@@ -1097,137 +1241,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="5">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="7">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="6">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="7">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="0">
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1265,6 +1409,27 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -1597,7 +1762,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L93"/>
+  <dimension ref="A1:L135"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="3" max="3" width="24.5" customWidth="1"/>
@@ -3535,233 +3700,1219 @@
         <v>74</v>
       </c>
     </row>
+    <row r="94" ht="16.5" spans="1:6">
+      <c r="A94">
+        <v>90</v>
+      </c>
+      <c r="B94">
+        <v>1</v>
+      </c>
+      <c r="C94" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="D94" s="3">
+        <v>1100700299</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F94" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="95" ht="16.5" spans="1:6">
+      <c r="A95">
+        <v>91</v>
+      </c>
+      <c r="B95">
+        <v>1</v>
+      </c>
+      <c r="C95" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="D95" s="15">
+        <v>2041092199</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F95" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="96" ht="16.5" spans="1:6">
+      <c r="A96">
+        <v>92</v>
+      </c>
+      <c r="B96">
+        <v>1</v>
+      </c>
+      <c r="C96" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="D96" s="15">
+        <v>2061092199</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F96" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="97" ht="16.5" spans="1:7">
+      <c r="A97">
+        <v>93</v>
+      </c>
+      <c r="B97">
+        <v>1</v>
+      </c>
+      <c r="C97" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="D97" s="15">
+        <v>2081092199</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F97" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="98" ht="16.5" spans="1:7">
+      <c r="A98">
+        <v>94</v>
+      </c>
+      <c r="B98">
+        <v>1</v>
+      </c>
+      <c r="C98" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="D98" s="15">
+        <v>2071092199</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F98" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="99" ht="16.5" spans="1:7">
+      <c r="A99">
+        <v>95</v>
+      </c>
+      <c r="B99">
+        <v>1</v>
+      </c>
+      <c r="C99" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="D99" s="15">
+        <v>2091092199</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F99" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="100" ht="16.5" spans="1:7">
+      <c r="A100">
+        <v>96</v>
+      </c>
+      <c r="B100">
+        <v>1</v>
+      </c>
+      <c r="C100" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="D100" s="15">
+        <v>2042092199</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F100" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="101" ht="16.5" spans="1:7">
+      <c r="A101">
+        <v>97</v>
+      </c>
+      <c r="B101">
+        <v>1</v>
+      </c>
+      <c r="C101" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="D101" s="15">
+        <v>2062092199</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F101" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="102" ht="16.5" spans="1:7">
+      <c r="A102">
+        <v>98</v>
+      </c>
+      <c r="B102">
+        <v>1</v>
+      </c>
+      <c r="C102" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="D102" s="15">
+        <v>2082092199</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F102" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="103" ht="16.5" spans="1:7">
+      <c r="A103">
+        <v>99</v>
+      </c>
+      <c r="B103">
+        <v>1</v>
+      </c>
+      <c r="C103" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="D103" s="15">
+        <v>2072092199</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F103" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="104" ht="16.5" spans="1:7">
+      <c r="A104">
+        <v>100</v>
+      </c>
+      <c r="B104">
+        <v>1</v>
+      </c>
+      <c r="C104" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="D104" s="15">
+        <v>2092092199</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F104" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="105" ht="16.5" spans="1:7">
+      <c r="A105">
+        <v>101</v>
+      </c>
+      <c r="B105">
+        <v>1</v>
+      </c>
+      <c r="C105" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="D105" s="15">
+        <v>2043052199</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F105" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="106" ht="16.5" spans="1:7">
+      <c r="A106">
+        <v>102</v>
+      </c>
+      <c r="B106">
+        <v>1</v>
+      </c>
+      <c r="C106" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="D106" s="15">
+        <v>2063052199</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F106" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="107" ht="16.5" spans="1:7">
+      <c r="A107">
+        <v>103</v>
+      </c>
+      <c r="B107">
+        <v>1</v>
+      </c>
+      <c r="C107" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="D107" s="15">
+        <v>2083052199</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F107" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="108" ht="16.5" spans="1:7">
+      <c r="A108">
+        <v>104</v>
+      </c>
+      <c r="B108">
+        <v>1</v>
+      </c>
+      <c r="C108" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="D108" s="15">
+        <v>2073052199</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F108" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="109" ht="16.5" spans="1:7">
+      <c r="A109">
+        <v>105</v>
+      </c>
+      <c r="B109">
+        <v>1</v>
+      </c>
+      <c r="C109" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="D109" s="15">
+        <v>2093052199</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F109" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="110" ht="16.5" spans="1:7">
+      <c r="A110">
+        <v>106</v>
+      </c>
+      <c r="B110">
+        <v>1</v>
+      </c>
+      <c r="C110" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="D110" s="15">
+        <v>1280036699</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F110" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="111" ht="16.5" spans="1:7">
+      <c r="A111">
+        <v>107</v>
+      </c>
+      <c r="B111">
+        <v>1</v>
+      </c>
+      <c r="C111" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="D111" s="15">
+        <v>1280036799</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F111" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="112" ht="16.5" spans="1:7">
+      <c r="A112">
+        <v>108</v>
+      </c>
+      <c r="B112">
+        <v>1</v>
+      </c>
+      <c r="C112" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="D112" s="15">
+        <v>1280036999</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F112" t="s">
+        <v>54</v>
+      </c>
+      <c r="G112" s="15"/>
+    </row>
+    <row r="113" ht="16.5" spans="1:6">
+      <c r="A113">
+        <v>109</v>
+      </c>
+      <c r="B113">
+        <v>1</v>
+      </c>
+      <c r="C113" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="D113" s="15">
+        <v>1280036899</v>
+      </c>
+      <c r="E113" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F113" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="114" ht="16.5" spans="1:6">
+      <c r="A114">
+        <v>110</v>
+      </c>
+      <c r="B114">
+        <v>1</v>
+      </c>
+      <c r="C114" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="D114" s="15">
+        <v>2031062199</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F114" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="115" ht="16.5" spans="1:6">
+      <c r="A115">
+        <v>111</v>
+      </c>
+      <c r="B115">
+        <v>1</v>
+      </c>
+      <c r="C115" s="16" t="s">
+        <v>161</v>
+      </c>
+      <c r="D115" s="15">
+        <v>2031072199</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F115" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="116" ht="16.5" spans="1:6">
+      <c r="A116">
+        <v>112</v>
+      </c>
+      <c r="B116">
+        <v>1</v>
+      </c>
+      <c r="C116" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="D116" s="15">
+        <v>202199</v>
+      </c>
+      <c r="E116" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F116" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="117" ht="16.5" spans="1:6">
+      <c r="A117">
+        <v>113</v>
+      </c>
+      <c r="B117">
+        <v>1</v>
+      </c>
+      <c r="C117" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="D117" s="15">
+        <v>202399</v>
+      </c>
+      <c r="E117" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F117" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="118" ht="16.5" spans="1:6">
+      <c r="A118">
+        <v>114</v>
+      </c>
+      <c r="B118">
+        <v>1</v>
+      </c>
+      <c r="C118" s="16" t="s">
+        <v>164</v>
+      </c>
+      <c r="D118" s="15">
+        <v>207699</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F118" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="119" ht="16.5" spans="1:6">
+      <c r="A119">
+        <v>115</v>
+      </c>
+      <c r="B119">
+        <v>1</v>
+      </c>
+      <c r="C119" s="16" t="s">
+        <v>165</v>
+      </c>
+      <c r="D119" s="17">
+        <v>2013102199</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F119" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="120" ht="16.5" spans="1:6">
+      <c r="A120">
+        <v>116</v>
+      </c>
+      <c r="B120">
+        <v>1</v>
+      </c>
+      <c r="C120" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="D120" s="17">
+        <v>2013052199</v>
+      </c>
+      <c r="E120" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F120" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="121" ht="16.5" spans="1:6">
+      <c r="A121">
+        <v>117</v>
+      </c>
+      <c r="B121">
+        <v>1</v>
+      </c>
+      <c r="C121" s="16" t="s">
+        <v>167</v>
+      </c>
+      <c r="D121" s="15">
+        <v>2012092199</v>
+      </c>
+      <c r="E121" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F121" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="122" ht="16.5" spans="1:6">
+      <c r="A122">
+        <v>118</v>
+      </c>
+      <c r="B122">
+        <v>1</v>
+      </c>
+      <c r="C122" s="18" t="s">
+        <v>168</v>
+      </c>
+      <c r="D122" s="19">
+        <v>2076132199</v>
+      </c>
+      <c r="E122" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F122" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="123" ht="16.5" spans="1:6">
+      <c r="A123">
+        <v>119</v>
+      </c>
+      <c r="B123">
+        <v>1</v>
+      </c>
+      <c r="C123" s="20" t="s">
+        <v>169</v>
+      </c>
+      <c r="D123" s="19">
+        <v>2085102199</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F123" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="124" ht="16.5" spans="1:6">
+      <c r="A124">
+        <v>120</v>
+      </c>
+      <c r="B124">
+        <v>1</v>
+      </c>
+      <c r="C124" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="D124" s="19">
+        <v>2075102199</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F124" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="125" ht="16.5" spans="1:6">
+      <c r="A125">
+        <v>121</v>
+      </c>
+      <c r="B125">
+        <v>1</v>
+      </c>
+      <c r="C125" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="D125" s="19">
+        <v>2066082199</v>
+      </c>
+      <c r="E125" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F125" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="126" ht="16.5" spans="1:6">
+      <c r="A126">
+        <v>122</v>
+      </c>
+      <c r="B126">
+        <v>1</v>
+      </c>
+      <c r="C126" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="D126" s="19">
+        <v>2066082299</v>
+      </c>
+      <c r="E126" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F126" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="127" ht="16.5" spans="1:6">
+      <c r="A127">
+        <v>123</v>
+      </c>
+      <c r="B127">
+        <v>1</v>
+      </c>
+      <c r="C127" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="D127" s="19">
+        <v>2066082399</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F127" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="128" ht="16.5" spans="1:6">
+      <c r="A128">
+        <v>124</v>
+      </c>
+      <c r="B128">
+        <v>1</v>
+      </c>
+      <c r="C128" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="D128" s="19">
+        <v>2066082499</v>
+      </c>
+      <c r="E128" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F128" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="129" ht="16.5" spans="1:6">
+      <c r="A129">
+        <v>125</v>
+      </c>
+      <c r="B129">
+        <v>1</v>
+      </c>
+      <c r="C129" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="D129" s="19">
+        <v>2066082599</v>
+      </c>
+      <c r="E129" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F129" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="130" ht="16.5" spans="1:6">
+      <c r="A130">
+        <v>126</v>
+      </c>
+      <c r="B130">
+        <v>1</v>
+      </c>
+      <c r="C130" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="D130" s="21">
+        <v>2055082199</v>
+      </c>
+      <c r="E130" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F130" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="131" ht="16.5" spans="1:6">
+      <c r="A131">
+        <v>127</v>
+      </c>
+      <c r="B131">
+        <v>1</v>
+      </c>
+      <c r="C131" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="D131" s="21">
+        <v>2055082299</v>
+      </c>
+      <c r="E131" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F131" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="132" ht="16.5" spans="1:6">
+      <c r="A132">
+        <v>128</v>
+      </c>
+      <c r="B132">
+        <v>1</v>
+      </c>
+      <c r="C132" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="D132" s="21">
+        <v>2055082399</v>
+      </c>
+      <c r="E132" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F132" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="133" ht="16.5" spans="1:6">
+      <c r="A133">
+        <v>129</v>
+      </c>
+      <c r="B133">
+        <v>1</v>
+      </c>
+      <c r="C133" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="D133" s="21">
+        <v>2055082499</v>
+      </c>
+      <c r="E133" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F133" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="134" ht="16.5" spans="1:6">
+      <c r="A134">
+        <v>130</v>
+      </c>
+      <c r="B134">
+        <v>1</v>
+      </c>
+      <c r="C134" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="D134" s="21">
+        <v>2055082599</v>
+      </c>
+      <c r="E134" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F134" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="135" ht="16.5" spans="1:6">
+      <c r="A135">
+        <v>131</v>
+      </c>
+      <c r="B135">
+        <v>1</v>
+      </c>
+      <c r="C135" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="D135" s="12">
+        <v>2027052199</v>
+      </c>
+      <c r="E135" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F135" t="s">
+        <v>50</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="D5">
-    <cfRule type="duplicateValues" dxfId="0" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="150"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6">
-    <cfRule type="duplicateValues" dxfId="0" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="149"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D7">
+    <cfRule type="duplicateValues" dxfId="0" priority="133"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="132"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E7">
+    <cfRule type="duplicateValues" dxfId="0" priority="135"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="134"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C16">
+    <cfRule type="duplicateValues" dxfId="1" priority="138"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="139"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D28">
+    <cfRule type="duplicateValues" dxfId="1" priority="203"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="204"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D29">
+    <cfRule type="duplicateValues" dxfId="1" priority="201"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="202"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D30">
+    <cfRule type="duplicateValues" dxfId="1" priority="199"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="200"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D39">
+    <cfRule type="duplicateValues" dxfId="1" priority="193"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="194"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D40">
+    <cfRule type="duplicateValues" dxfId="1" priority="191"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="192"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D41">
+    <cfRule type="duplicateValues" dxfId="1" priority="189"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="190"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D42">
+    <cfRule type="duplicateValues" dxfId="1" priority="187"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="188"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D46">
+    <cfRule type="duplicateValues" dxfId="1" priority="183"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="184"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D47">
+    <cfRule type="duplicateValues" dxfId="1" priority="181"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="182"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D48">
+    <cfRule type="duplicateValues" dxfId="1" priority="179"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="180"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D49">
+    <cfRule type="duplicateValues" dxfId="1" priority="177"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="178"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D50">
+    <cfRule type="duplicateValues" dxfId="1" priority="175"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="176"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D51">
+    <cfRule type="duplicateValues" dxfId="1" priority="173"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="174"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D52">
+    <cfRule type="duplicateValues" dxfId="1" priority="171"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="172"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D53">
+    <cfRule type="duplicateValues" dxfId="1" priority="169"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="170"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D54">
+    <cfRule type="duplicateValues" dxfId="1" priority="167"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="168"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D55">
+    <cfRule type="duplicateValues" dxfId="1" priority="165"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="166"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D56">
+    <cfRule type="duplicateValues" dxfId="1" priority="163"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="164"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D57">
+    <cfRule type="duplicateValues" dxfId="1" priority="161"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="162"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D58">
+    <cfRule type="duplicateValues" dxfId="1" priority="159"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="160"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D59">
+    <cfRule type="duplicateValues" dxfId="1" priority="157"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="158"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D60">
+    <cfRule type="duplicateValues" dxfId="1" priority="155"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="156"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D61">
+    <cfRule type="duplicateValues" dxfId="1" priority="153"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="154"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D62">
+    <cfRule type="duplicateValues" dxfId="1" priority="151"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="152"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D63">
+    <cfRule type="duplicateValues" dxfId="0" priority="131"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="130"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D64">
+    <cfRule type="duplicateValues" dxfId="0" priority="129"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="128"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C70">
+    <cfRule type="duplicateValues" dxfId="1" priority="120"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D70">
+    <cfRule type="duplicateValues" dxfId="0" priority="123"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="122"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E70">
+    <cfRule type="duplicateValues" dxfId="1" priority="126"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D84">
+    <cfRule type="duplicateValues" dxfId="0" priority="103"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="102"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D85">
+    <cfRule type="duplicateValues" dxfId="0" priority="101"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="100"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D86">
+    <cfRule type="duplicateValues" dxfId="0" priority="99"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="98"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D87">
+    <cfRule type="duplicateValues" dxfId="0" priority="97"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="96"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D88">
+    <cfRule type="duplicateValues" dxfId="0" priority="95"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="94"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D89">
+    <cfRule type="duplicateValues" dxfId="0" priority="93"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="92"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D90">
+    <cfRule type="duplicateValues" dxfId="0" priority="91"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="90"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D91">
+    <cfRule type="duplicateValues" dxfId="0" priority="89"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="88"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D92">
+    <cfRule type="duplicateValues" dxfId="0" priority="87"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="86"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D93">
+    <cfRule type="duplicateValues" dxfId="0" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="84"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D94">
+    <cfRule type="duplicateValues" dxfId="0" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="82"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D95">
+    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D96">
+    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D97">
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D98">
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D99">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D100">
+    <cfRule type="duplicateValues" dxfId="0" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D101">
+    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D102">
+    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D103">
+    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D104">
+    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D105">
+    <cfRule type="duplicateValues" dxfId="0" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="31"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D106">
+    <cfRule type="duplicateValues" dxfId="0" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="29"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D107">
+    <cfRule type="duplicateValues" dxfId="0" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="27"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D108">
+    <cfRule type="duplicateValues" dxfId="0" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="25"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D109">
+    <cfRule type="duplicateValues" dxfId="0" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="23"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G112">
+    <cfRule type="duplicateValues" dxfId="0" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="35"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D113">
+    <cfRule type="duplicateValues" dxfId="0" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="33"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D114">
+    <cfRule type="duplicateValues" dxfId="0" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="39"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D115">
+    <cfRule type="duplicateValues" dxfId="0" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="41"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D116">
+    <cfRule type="duplicateValues" dxfId="0" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="43"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D117">
+    <cfRule type="duplicateValues" dxfId="0" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="45"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D118">
+    <cfRule type="duplicateValues" dxfId="0" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="47"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D121">
     <cfRule type="duplicateValues" dxfId="0" priority="50"/>
     <cfRule type="duplicateValues" dxfId="1" priority="49"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E7">
+  <conditionalFormatting sqref="C122">
+    <cfRule type="duplicateValues" dxfId="1" priority="76"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D122">
+    <cfRule type="duplicateValues" dxfId="0" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="61"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C123">
+    <cfRule type="duplicateValues" dxfId="1" priority="79"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D123">
+    <cfRule type="duplicateValues" dxfId="0" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="59"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C124">
+    <cfRule type="duplicateValues" dxfId="1" priority="71"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D124">
+    <cfRule type="duplicateValues" dxfId="0" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="57"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C135">
+    <cfRule type="duplicateValues" dxfId="1" priority="80"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D135">
     <cfRule type="duplicateValues" dxfId="0" priority="52"/>
     <cfRule type="duplicateValues" dxfId="1" priority="51"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C16">
-    <cfRule type="duplicateValues" dxfId="1" priority="55"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="56"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D28">
-    <cfRule type="duplicateValues" dxfId="1" priority="120"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="121"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D29">
+  <conditionalFormatting sqref="C17:C19">
+    <cfRule type="duplicateValues" dxfId="1" priority="136"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="137"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C65:C69">
+    <cfRule type="duplicateValues" dxfId="1" priority="121"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C114:C121">
+    <cfRule type="duplicateValues" dxfId="1" priority="81"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C125:C129">
+    <cfRule type="duplicateValues" dxfId="1" priority="68"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C130:C134">
+    <cfRule type="duplicateValues" dxfId="1" priority="65"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D5:D6">
+    <cfRule type="duplicateValues" dxfId="1" priority="148"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8:D15">
+    <cfRule type="duplicateValues" dxfId="1" priority="144"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="145"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D16:D19">
+    <cfRule type="duplicateValues" dxfId="1" priority="140"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="141"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D20:D27">
+    <cfRule type="duplicateValues" dxfId="0" priority="205"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D31:D38">
+    <cfRule type="duplicateValues" dxfId="0" priority="195"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D43:D45">
+    <cfRule type="duplicateValues" dxfId="1" priority="185"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="186"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D65:D69">
+    <cfRule type="duplicateValues" dxfId="0" priority="125"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="124"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D71:D75">
+    <cfRule type="duplicateValues" dxfId="0" priority="119"/>
     <cfRule type="duplicateValues" dxfId="1" priority="118"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="119"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D30">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D76:D79">
     <cfRule type="duplicateValues" dxfId="1" priority="116"/>
     <cfRule type="duplicateValues" dxfId="0" priority="117"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D39">
-    <cfRule type="duplicateValues" dxfId="1" priority="110"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="111"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D40">
-    <cfRule type="duplicateValues" dxfId="1" priority="108"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="109"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D41">
-    <cfRule type="duplicateValues" dxfId="1" priority="106"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="107"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D42">
+  <conditionalFormatting sqref="D80:D83">
+    <cfRule type="duplicateValues" dxfId="0" priority="105"/>
     <cfRule type="duplicateValues" dxfId="1" priority="104"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="105"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D46">
-    <cfRule type="duplicateValues" dxfId="1" priority="100"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="101"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D47">
-    <cfRule type="duplicateValues" dxfId="1" priority="98"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="99"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D48">
-    <cfRule type="duplicateValues" dxfId="1" priority="96"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="97"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D49">
-    <cfRule type="duplicateValues" dxfId="1" priority="94"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="95"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D50">
-    <cfRule type="duplicateValues" dxfId="1" priority="92"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="93"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D51">
-    <cfRule type="duplicateValues" dxfId="1" priority="90"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="91"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D52">
-    <cfRule type="duplicateValues" dxfId="1" priority="88"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="89"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D53">
-    <cfRule type="duplicateValues" dxfId="1" priority="86"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="87"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D54">
-    <cfRule type="duplicateValues" dxfId="1" priority="84"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="85"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D55">
-    <cfRule type="duplicateValues" dxfId="1" priority="82"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="83"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D56">
-    <cfRule type="duplicateValues" dxfId="1" priority="80"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="81"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D57">
-    <cfRule type="duplicateValues" dxfId="1" priority="78"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="79"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D58">
-    <cfRule type="duplicateValues" dxfId="1" priority="76"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="77"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D59">
-    <cfRule type="duplicateValues" dxfId="1" priority="74"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="75"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D60">
-    <cfRule type="duplicateValues" dxfId="1" priority="72"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="73"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D61">
-    <cfRule type="duplicateValues" dxfId="1" priority="70"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="71"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D62">
-    <cfRule type="duplicateValues" dxfId="1" priority="68"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="69"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D63">
-    <cfRule type="duplicateValues" dxfId="0" priority="48"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="47"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D64">
-    <cfRule type="duplicateValues" dxfId="0" priority="46"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="45"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C70">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D110:D112">
+    <cfRule type="duplicateValues" dxfId="0" priority="38"/>
     <cfRule type="duplicateValues" dxfId="1" priority="37"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D70">
-    <cfRule type="duplicateValues" dxfId="0" priority="40"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="39"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E70">
-    <cfRule type="duplicateValues" dxfId="1" priority="43"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D84">
-    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="19"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D85">
-    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="17"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D86">
-    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="15"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D87">
-    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="13"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D88">
-    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D89">
-    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D90">
-    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="7"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D91">
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D92">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D93">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C17:C19">
+  <conditionalFormatting sqref="D125:D129">
+    <cfRule type="duplicateValues" dxfId="0" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="55"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D130:D134">
+    <cfRule type="duplicateValues" dxfId="0" priority="54"/>
     <cfRule type="duplicateValues" dxfId="1" priority="53"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="54"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C65:C69">
-    <cfRule type="duplicateValues" dxfId="1" priority="38"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D5:D6">
-    <cfRule type="duplicateValues" dxfId="1" priority="65"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D8:D15">
-    <cfRule type="duplicateValues" dxfId="1" priority="61"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="62"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D16:D19">
-    <cfRule type="duplicateValues" dxfId="1" priority="57"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="58"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D20:D27">
-    <cfRule type="duplicateValues" dxfId="0" priority="122"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D31:D38">
-    <cfRule type="duplicateValues" dxfId="0" priority="112"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D43:D45">
-    <cfRule type="duplicateValues" dxfId="1" priority="102"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="103"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D65:D69">
-    <cfRule type="duplicateValues" dxfId="0" priority="42"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="41"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D71:D75">
-    <cfRule type="duplicateValues" dxfId="0" priority="36"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="35"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D76:D79">
-    <cfRule type="duplicateValues" dxfId="1" priority="33"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="34"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D80:D83">
-    <cfRule type="duplicateValues" dxfId="0" priority="22"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8:E15">
-    <cfRule type="duplicateValues" dxfId="1" priority="63"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="146"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="147"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E16:E19">
-    <cfRule type="duplicateValues" dxfId="1" priority="59"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="142"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="143"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E65:E69">
-    <cfRule type="duplicateValues" dxfId="1" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="127"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -3792,7 +4943,7 @@
         <v>18888</v>
       </c>
       <c r="F1" t="s">
-        <v>141</v>
+        <v>182</v>
       </c>
     </row>
     <row r="2" ht="16.5" spans="1:6">
@@ -3812,7 +4963,7 @@
         <v>8888</v>
       </c>
       <c r="F2" t="s">
-        <v>142</v>
+        <v>183</v>
       </c>
     </row>
     <row r="3" ht="16.5" spans="1:6">
@@ -3832,7 +4983,7 @@
         <v>5888</v>
       </c>
       <c r="F3" t="s">
-        <v>143</v>
+        <v>184</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:6">
@@ -3852,7 +5003,7 @@
         <v>3888</v>
       </c>
       <c r="F4" t="s">
-        <v>144</v>
+        <v>185</v>
       </c>
     </row>
     <row r="5" ht="16.5" spans="1:6">
@@ -3872,7 +5023,7 @@
         <v>2888</v>
       </c>
       <c r="F5" t="s">
-        <v>145</v>
+        <v>186</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:6">
@@ -3892,7 +5043,7 @@
         <v>1888</v>
       </c>
       <c r="F6" t="s">
-        <v>146</v>
+        <v>187</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:6">
@@ -3912,7 +5063,7 @@
         <v>888</v>
       </c>
       <c r="F7" t="s">
-        <v>147</v>
+        <v>188</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:6">
@@ -3932,7 +5083,7 @@
         <v>588</v>
       </c>
       <c r="F8" t="s">
-        <v>148</v>
+        <v>189</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:6">
@@ -3952,7 +5103,7 @@
         <v>188</v>
       </c>
       <c r="F9" t="s">
-        <v>149</v>
+        <v>190</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:6">
@@ -3972,7 +5123,7 @@
         <v>1000000</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>150</v>
+        <v>191</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:6">
@@ -3992,7 +5143,7 @@
         <v>3000000</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>151</v>
+        <v>192</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:6">
@@ -4012,7 +5163,7 @@
         <v>5000000</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>152</v>
+        <v>193</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:6">
@@ -4032,7 +5183,7 @@
         <v>10000000</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>153</v>
+        <v>194</v>
       </c>
     </row>
   </sheetData>
